--- a/free-sales-cleanup-template/sales-cleanup-template.xlsx
+++ b/free-sales-cleanup-template/sales-cleanup-template.xlsx
@@ -41,7 +41,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="009AA0A6"/>
+      <color rgb="006E6555"/>
       <sz val="9"/>
     </font>
     <font>
@@ -51,21 +51,21 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="005C5645"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F2933"/>
+      <color rgb="00211D14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F2933"/>
+      <color rgb="00211D14"/>
       <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B6E4F"/>
+      <color rgb="001E7A47"/>
       <sz val="13"/>
     </font>
     <font>
@@ -75,7 +75,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="005C5645"/>
       <sz val="9"/>
     </font>
     <font>
@@ -84,11 +84,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B6E4F"/>
+      <color rgb="001E7A47"/>
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -97,27 +97,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2933"/>
+        <fgColor rgb="00211D14"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F2"/>
+        <fgColor rgb="00F4F1E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECE8DE"/>
+        <fgColor rgb="00E4DFD1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6F2EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F5EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +126,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D9D4C9"/>
+        <color rgb="00E4DFD1"/>
       </bottom>
     </border>
   </borders>
@@ -180,11 +175,11 @@
     <xf numFmtId="166" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,7 +188,7 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>

--- a/free-sales-cleanup-template/sales-cleanup-template.xlsx
+++ b/free-sales-cleanup-template/sales-cleanup-template.xlsx
@@ -1437,7 +1437,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  free template</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  free template</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  free template</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  free template</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  free template</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  free template</t>
         </is>
       </c>
     </row>
